--- a/ig/hospitalnotification/StructureDefinition-medcom-messaging-reportOfAdmissionExtension.xlsx
+++ b/ig/hospitalnotification/StructureDefinition-medcom-messaging-reportOfAdmissionExtension.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>3.0.1</t>
+    <t>3.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-03-02T09:56:15+01:00</t>
+    <t>2026-02-10T12:55:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>MedCom (http://www.medcom.dk)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -260,6 +260,10 @@
 </t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+  </si>
+  <si>
     <t>Extension.id</t>
   </si>
   <si>
@@ -303,10 +307,6 @@
   </si>
   <si>
     <t>Element.extension</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Extension.url</t>
@@ -464,10 +464,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyFont="true">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyBorder="true" applyFill="true" applyAlignment="true" applyFont="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="true" applyAlignment="true">
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
@@ -655,42 +655,42 @@
   <dimension ref="A1:AK6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="19.00390625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="19.00390625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="11.1328125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="7.68359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="16.80078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="16.80078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="9.734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="8.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.91015625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.9140625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="17.07421875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0390625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="17.7265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="15.59375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="22.67578125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -903,7 +903,7 @@
         <v>80</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AK2" t="s" s="2">
         <v>76</v>
@@ -911,10 +911,10 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -925,7 +925,7 @@
         <v>77</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>76</v>
@@ -937,13 +937,13 @@
         <v>76</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -994,13 +994,13 @@
         <v>76</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>76</v>
@@ -1009,15 +1009,15 @@
         <v>76</v>
       </c>
       <c r="AK3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1040,13 +1040,13 @@
         <v>76</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="L4" t="s" s="2">
         <v>30</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1085,19 +1085,19 @@
         <v>76</v>
       </c>
       <c r="AB4" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="AC4" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AD4" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>77</v>
@@ -1109,7 +1109,7 @@
         <v>76</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>76</v>
@@ -1128,10 +1128,10 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>76</v>
@@ -1205,10 +1205,10 @@
         <v>96</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>76</v>
@@ -1233,10 +1233,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>76</v>
@@ -1311,7 +1311,7 @@
         <v>77</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>76</v>
